--- a/astro-site/public/dl/restaurant-checklist-templates/02-kitchen-station-checklists.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/02-kitchen-station-checklists.xlsx
@@ -813,7 +813,7 @@
     <row r="29" ht="31" customHeight="1">
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
     <row r="33" ht="47" customHeight="1">
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>▸ You are in 02-kitchen-station-checklists.xlsx: it is one MORE layer, not a repeat — the frame of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
+          <t>▸ You are in 02-kitchen-station-checklists.xlsx: it is one MORE layer, not a repeat — the backbone of the day is in 08-restaurant-opening-closing-checklist.xlsx and 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>Store leftover proteins: label and date</t>
+          <t>Cool leftover proteins fast (135 → 70 °F within 2 h, then to 41 °F within 4 more h, FDA Food Code 3-501.14), then label and date</t>
         </is>
       </c>
       <c r="C23" s="29" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Turn off the fryer when done and filter the oil ONLY below 104 °F, never hot, with gloves and a stable container; put used oil in the used cooking oil recycler's container</t>
+          <t>Turn off the fryer when done; filter the oil per the fryer manufacturer's procedure (built-in filters run at operating temperature; if filtering by hand, let it cool first, wear heat-resistant gloves and use a stable container); put used oil in the used cooking oil recycler's container</t>
         </is>
       </c>
       <c r="C27" s="29" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Raw or undercooked fish (tartare, ceviche, crudo) — parasite destruction: confirm it was frozen at −4 °F for 7 days (or −31 °F until solid + 15 h); keep the record 90 days (FDA Food Code 3-402.11)</t>
+          <t>Raw or undercooked fish (tartare, ceviche, crudo) — parasite destruction: confirm it was frozen at −4 °F or below for 7 days (or −31 °F or below until solid + 15 h); keep the record 90 days (FDA Food Code 3-402.11)</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>Portion carpaccio, ceviche, tartare</t>
+          <t>Portion carpaccio, ceviche, tartare (menu carries the raw/undercooked consumer advisory, FDA 3-603.11)</t>
         </is>
       </c>
       <c r="C11" s="29" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Date: ___/___/______    Shift: ☐ AM  ☐ PM  ☐ Overnight    Shift manager: _________________________</t>
+          <t>Date: ___/___/______    Shift: ☐ AM  ☐ Mid  ☐ PM    Shift manager: _________________________</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Raw or undercooked fish and shellfish — fish: frozen for parasites (−4 °F 7 days or −31 °F + 15 h, FDA Food Code 3-402.11), record kept 90 days; raw oysters and clams: shellstock tags kept 90 days</t>
+          <t>Raw or undercooked fish and shellfish — fish: frozen for parasites (−4 °F or below 7 days, or −31 °F or below + 15 h, FDA Food Code 3-402.11), record kept 90 days; raw oysters and clams: shellstock tags kept 90 days</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">

--- a/astro-site/public/dl/restaurant-checklist-templates/02-kitchen-station-checklists.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/02-kitchen-station-checklists.xlsx
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Raw or undercooked fish (tartare, ceviche, crudo) — parasite destruction: confirm it was frozen at −4 °F or below for 7 days (or −31 °F or below until solid + 15 h); keep the record 90 days (FDA Food Code 3-402.11)</t>
+          <t>Raw or undercooked fish (tartare, ceviche, crudo) — parasite destruction (FDA Food Code 3-402.11): confirm it was frozen and stored at −4 °F or below for 7 days, or frozen at −31 °F or below until solid and stored at −31 °F or below for 15 h, or frozen at −31 °F or below until solid and stored at −4 °F or below for 24 h; keep the record 90 days (FDA Food Code 3-402.12)</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Raw or undercooked fish and shellfish — fish: frozen for parasites (−4 °F or below 7 days, or −31 °F or below + 15 h, FDA Food Code 3-402.11), record kept 90 days; raw oysters and clams: shellstock tags kept 90 days</t>
+          <t>Raw or undercooked fish and shellfish — fish: frozen for parasites (−4 °F or below for 7 days; or −31 °F or below until solid, then 15 h at −31 °F or below or 24 h at −4 °F or below; FDA Food Code 3-402.11), record kept 90 days (FDA Food Code 3-402.12); raw oysters and clams: shellstock tags kept 90 days</t>
         </is>
       </c>
       <c r="C10" s="29" t="inlineStr">
